--- a/outputs/06_测试数据/发动机主线业务流程-多工厂一级工艺版/导入包/系统配置_模板.xlsx
+++ b/outputs/06_测试数据/发动机主线业务流程-多工厂一级工艺版/导入包/系统配置_模板.xlsx
@@ -696,7 +696,7 @@
       </c>
       <c r="C2" s="17" t="inlineStr">
         <is>
-          <t>Adm001</t>
+          <t>ADM-CORP-001</t>
         </is>
       </c>
       <c r="D2" s="17" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="I2" s="17" t="inlineStr">
         <is>
-          <t>Adm001</t>
+          <t>ADM-CORP-001</t>
         </is>
       </c>
       <c r="J2" s="17" t="inlineStr"/>
@@ -730,28 +730,28 @@
     <row r="3">
       <c r="A3" s="17" t="inlineStr">
         <is>
-          <t>Adm001</t>
+          <t>ADM-CORP-001</t>
         </is>
       </c>
       <c r="B3" s="17" t="inlineStr">
         <is>
-          <t>工厂</t>
+          <t>部门</t>
         </is>
       </c>
       <c r="C3" s="17" t="inlineStr">
         <is>
-          <t>Adm010</t>
+          <t>ADM-PD-001</t>
         </is>
       </c>
       <c r="D3" s="17" t="inlineStr">
         <is>
-          <t>10-机加厂</t>
+          <t>生产部</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr"/>
       <c r="F3" s="17" t="inlineStr">
         <is>
-          <t>机加厂</t>
+          <t>生产部</t>
         </is>
       </c>
       <c r="G3" s="17" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="I3" s="17" t="inlineStr">
         <is>
-          <t>Adm010</t>
+          <t>ADM-PD-001</t>
         </is>
       </c>
       <c r="J3" s="17" t="inlineStr"/>
@@ -774,7 +774,7 @@
     <row r="4">
       <c r="A4" s="17" t="inlineStr">
         <is>
-          <t>Adm001</t>
+          <t>ADM-CORP-001</t>
         </is>
       </c>
       <c r="B4" s="17" t="inlineStr">
@@ -784,18 +784,18 @@
       </c>
       <c r="C4" s="17" t="inlineStr">
         <is>
-          <t>Adm020</t>
+          <t>ADM-MC-001</t>
         </is>
       </c>
       <c r="D4" s="17" t="inlineStr">
         <is>
-          <t>20-盘轴厂</t>
+          <t>10-机加厂</t>
         </is>
       </c>
       <c r="E4" s="17" t="inlineStr"/>
       <c r="F4" s="17" t="inlineStr">
         <is>
-          <t>盘轴厂</t>
+          <t>机加厂</t>
         </is>
       </c>
       <c r="G4" s="17" t="inlineStr">
@@ -810,7 +810,7 @@
       </c>
       <c r="I4" s="17" t="inlineStr">
         <is>
-          <t>Adm020</t>
+          <t>ADM-MC-001</t>
         </is>
       </c>
       <c r="J4" s="17" t="inlineStr"/>
@@ -818,7 +818,7 @@
     <row r="5">
       <c r="A5" s="17" t="inlineStr">
         <is>
-          <t>Adm001</t>
+          <t>ADM-CORP-001</t>
         </is>
       </c>
       <c r="B5" s="17" t="inlineStr">
@@ -828,18 +828,18 @@
       </c>
       <c r="C5" s="17" t="inlineStr">
         <is>
-          <t>Adm030</t>
+          <t>ADM-SH-001</t>
         </is>
       </c>
       <c r="D5" s="17" t="inlineStr">
         <is>
-          <t>30-叶片厂</t>
+          <t>20-盘轴厂</t>
         </is>
       </c>
       <c r="E5" s="17" t="inlineStr"/>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>叶片厂</t>
+          <t>盘轴厂</t>
         </is>
       </c>
       <c r="G5" s="17" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="I5" s="17" t="inlineStr">
         <is>
-          <t>Adm030</t>
+          <t>ADM-SH-001</t>
         </is>
       </c>
       <c r="J5" s="17" t="inlineStr"/>
@@ -862,7 +862,7 @@
     <row r="6">
       <c r="A6" s="17" t="inlineStr">
         <is>
-          <t>Adm001</t>
+          <t>ADM-CORP-001</t>
         </is>
       </c>
       <c r="B6" s="17" t="inlineStr">
@@ -872,18 +872,18 @@
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t>Adm040</t>
+          <t>ADM-BL-001</t>
         </is>
       </c>
       <c r="D6" s="17" t="inlineStr">
         <is>
-          <t>40-装配厂</t>
+          <t>30-叶片厂</t>
         </is>
       </c>
       <c r="E6" s="17" t="inlineStr"/>
       <c r="F6" s="17" t="inlineStr">
         <is>
-          <t>装配厂</t>
+          <t>叶片厂</t>
         </is>
       </c>
       <c r="G6" s="17" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="I6" s="17" t="inlineStr">
         <is>
-          <t>Adm040</t>
+          <t>ADM-BL-001</t>
         </is>
       </c>
       <c r="J6" s="17" t="inlineStr"/>
@@ -906,7 +906,7 @@
     <row r="7">
       <c r="A7" s="17" t="inlineStr">
         <is>
-          <t>Adm001</t>
+          <t>ADM-CORP-001</t>
         </is>
       </c>
       <c r="B7" s="17" t="inlineStr">
@@ -916,18 +916,18 @@
       </c>
       <c r="C7" s="17" t="inlineStr">
         <is>
-          <t>Adm900</t>
+          <t>ADM-AS-001</t>
         </is>
       </c>
       <c r="D7" s="17" t="inlineStr">
         <is>
-          <t>生产部</t>
+          <t>40-装配厂</t>
         </is>
       </c>
       <c r="E7" s="17" t="inlineStr"/>
       <c r="F7" s="17" t="inlineStr">
         <is>
-          <t>生产部</t>
+          <t>装配厂</t>
         </is>
       </c>
       <c r="G7" s="17" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="I7" s="17" t="inlineStr">
         <is>
-          <t>Adm900</t>
+          <t>ADM-AS-001</t>
         </is>
       </c>
       <c r="J7" s="17" t="inlineStr"/>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="C2" s="17" t="inlineStr">
         <is>
-          <t>Biz001</t>
+          <t>ORG-CORP-001</t>
         </is>
       </c>
       <c r="D2" s="17" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="E2" s="17" t="inlineStr">
         <is>
-          <t>发动机主线业务流程示例公司</t>
+          <t>发动机多工厂协同主线示例公司</t>
         </is>
       </c>
       <c r="F2" s="17" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="H2" s="17" t="inlineStr">
         <is>
-          <t>Adm001</t>
+          <t>ADM-CORP-001</t>
         </is>
       </c>
       <c r="I2" s="17" t="inlineStr"/>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="K2" s="17" t="inlineStr">
         <is>
-          <t>Biz001</t>
+          <t>ORG-CORP-001</t>
         </is>
       </c>
       <c r="L2" s="17" t="inlineStr"/>
@@ -2230,7 +2230,7 @@
     <row r="3">
       <c r="A3" s="17" t="inlineStr">
         <is>
-          <t>Biz001</t>
+          <t>ORG-CORP-001</t>
         </is>
       </c>
       <c r="B3" s="17" t="inlineStr">
@@ -2240,22 +2240,22 @@
       </c>
       <c r="C3" s="17" t="inlineStr">
         <is>
-          <t>Biz010</t>
+          <t>ORG-PD-001</t>
         </is>
       </c>
       <c r="D3" s="17" t="inlineStr">
         <is>
-          <t>10-机加厂</t>
+          <t>生产部</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>负责机匣类关键件机加与尺寸放行</t>
+          <t>承接厂际协同计划与一级工艺展开。</t>
         </is>
       </c>
       <c r="F3" s="17" t="inlineStr">
         <is>
-          <t>机加厂</t>
+          <t>生产部</t>
         </is>
       </c>
       <c r="G3" s="17" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="H3" s="17" t="inlineStr">
         <is>
-          <t>Adm010</t>
+          <t>ADM-PD-001</t>
         </is>
       </c>
       <c r="I3" s="17" t="inlineStr">
         <is>
-          <t>机械加工专业</t>
+          <t>装配专业</t>
         </is>
       </c>
       <c r="J3" s="17" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="K3" s="17" t="inlineStr">
         <is>
-          <t>Biz010</t>
+          <t>ORG-PD-001</t>
         </is>
       </c>
       <c r="L3" s="17" t="inlineStr"/>
@@ -2288,7 +2288,7 @@
     <row r="4">
       <c r="A4" s="17" t="inlineStr">
         <is>
-          <t>Biz010</t>
+          <t>ORG-CORP-001</t>
         </is>
       </c>
       <c r="B4" s="17" t="inlineStr">
@@ -2298,31 +2298,39 @@
       </c>
       <c r="C4" s="17" t="inlineStr">
         <is>
-          <t>Biz011</t>
+          <t>ORG-MC-001</t>
         </is>
       </c>
       <c r="D4" s="17" t="inlineStr">
         <is>
-          <t>机加车间</t>
-        </is>
-      </c>
-      <c r="E4" s="17" t="inlineStr"/>
+          <t>10-机加厂</t>
+        </is>
+      </c>
+      <c r="E4" s="17" t="inlineStr">
+        <is>
+          <t>负责机匣组件机加与尺寸放行。</t>
+        </is>
+      </c>
       <c r="F4" s="17" t="inlineStr">
         <is>
-          <t>机加车间</t>
+          <t>机加厂</t>
         </is>
       </c>
       <c r="G4" s="17" t="inlineStr">
         <is>
-          <t>车间</t>
+          <t>工厂</t>
         </is>
       </c>
       <c r="H4" s="17" t="inlineStr">
         <is>
-          <t>Adm010</t>
-        </is>
-      </c>
-      <c r="I4" s="17" t="inlineStr"/>
+          <t>ADM-MC-001</t>
+        </is>
+      </c>
+      <c r="I4" s="17" t="inlineStr">
+        <is>
+          <t>机械加工专业</t>
+        </is>
+      </c>
       <c r="J4" s="17" t="inlineStr">
         <is>
           <t>MOM-SEED</t>
@@ -2330,7 +2338,7 @@
       </c>
       <c r="K4" s="17" t="inlineStr">
         <is>
-          <t>Biz011</t>
+          <t>ORG-MC-001</t>
         </is>
       </c>
       <c r="L4" s="17" t="inlineStr"/>
@@ -2338,7 +2346,7 @@
     <row r="5">
       <c r="A5" s="17" t="inlineStr">
         <is>
-          <t>Biz011</t>
+          <t>ORG-MC-001</t>
         </is>
       </c>
       <c r="B5" s="17" t="inlineStr">
@@ -2348,28 +2356,28 @@
       </c>
       <c r="C5" s="17" t="inlineStr">
         <is>
-          <t>Biz012</t>
+          <t>ORG-MC-WS-001</t>
         </is>
       </c>
       <c r="D5" s="17" t="inlineStr">
         <is>
-          <t>机加班组</t>
+          <t>机加车间</t>
         </is>
       </c>
       <c r="E5" s="17" t="inlineStr"/>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>机加班组</t>
+          <t>机加车间</t>
         </is>
       </c>
       <c r="G5" s="17" t="inlineStr">
         <is>
-          <t>班组</t>
+          <t>车间</t>
         </is>
       </c>
       <c r="H5" s="17" t="inlineStr">
         <is>
-          <t>Adm010</t>
+          <t>ADM-MC-001</t>
         </is>
       </c>
       <c r="I5" s="17" t="inlineStr"/>
@@ -2380,7 +2388,7 @@
       </c>
       <c r="K5" s="17" t="inlineStr">
         <is>
-          <t>Biz012</t>
+          <t>ORG-MC-WS-001</t>
         </is>
       </c>
       <c r="L5" s="17" t="inlineStr"/>
@@ -2388,7 +2396,7 @@
     <row r="6">
       <c r="A6" s="17" t="inlineStr">
         <is>
-          <t>Biz011</t>
+          <t>ORG-MC-WS-001</t>
         </is>
       </c>
       <c r="B6" s="17" t="inlineStr">
@@ -2398,18 +2406,18 @@
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t>Biz013</t>
+          <t>ORG-MC-TM-001</t>
         </is>
       </c>
       <c r="D6" s="17" t="inlineStr">
         <is>
-          <t>机加检验班组</t>
+          <t>机加班组</t>
         </is>
       </c>
       <c r="E6" s="17" t="inlineStr"/>
       <c r="F6" s="17" t="inlineStr">
         <is>
-          <t>机加检验</t>
+          <t>机加班组</t>
         </is>
       </c>
       <c r="G6" s="17" t="inlineStr">
@@ -2419,7 +2427,7 @@
       </c>
       <c r="H6" s="17" t="inlineStr">
         <is>
-          <t>Adm010</t>
+          <t>ADM-MC-001</t>
         </is>
       </c>
       <c r="I6" s="17" t="inlineStr"/>
@@ -2430,7 +2438,7 @@
       </c>
       <c r="K6" s="17" t="inlineStr">
         <is>
-          <t>Biz013</t>
+          <t>ORG-MC-TM-001</t>
         </is>
       </c>
       <c r="L6" s="17" t="inlineStr"/>
@@ -2438,7 +2446,7 @@
     <row r="7">
       <c r="A7" s="17" t="inlineStr">
         <is>
-          <t>Biz001</t>
+          <t>ORG-MC-WS-001</t>
         </is>
       </c>
       <c r="B7" s="17" t="inlineStr">
@@ -2448,39 +2456,31 @@
       </c>
       <c r="C7" s="17" t="inlineStr">
         <is>
-          <t>Biz020</t>
+          <t>ORG-MC-QC-001</t>
         </is>
       </c>
       <c r="D7" s="17" t="inlineStr">
         <is>
-          <t>20-盘轴厂</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="inlineStr">
-        <is>
-          <t>负责盘轴类关键件加工、平衡与终检</t>
-        </is>
-      </c>
+          <t>机加检验组</t>
+        </is>
+      </c>
+      <c r="E7" s="17" t="inlineStr"/>
       <c r="F7" s="17" t="inlineStr">
         <is>
-          <t>盘轴厂</t>
+          <t>机加检验</t>
         </is>
       </c>
       <c r="G7" s="17" t="inlineStr">
         <is>
-          <t>工厂</t>
+          <t>班组</t>
         </is>
       </c>
       <c r="H7" s="17" t="inlineStr">
         <is>
-          <t>Adm020</t>
-        </is>
-      </c>
-      <c r="I7" s="17" t="inlineStr">
-        <is>
-          <t>机械加工专业</t>
-        </is>
-      </c>
+          <t>ADM-MC-001</t>
+        </is>
+      </c>
+      <c r="I7" s="17" t="inlineStr"/>
       <c r="J7" s="17" t="inlineStr">
         <is>
           <t>MOM-SEED</t>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="K7" s="17" t="inlineStr">
         <is>
-          <t>Biz020</t>
+          <t>ORG-MC-QC-001</t>
         </is>
       </c>
       <c r="L7" s="17" t="inlineStr"/>
@@ -2496,7 +2496,7 @@
     <row r="8">
       <c r="A8" s="17" t="inlineStr">
         <is>
-          <t>Biz020</t>
+          <t>ORG-CORP-001</t>
         </is>
       </c>
       <c r="B8" s="17" t="inlineStr">
@@ -2506,31 +2506,39 @@
       </c>
       <c r="C8" s="17" t="inlineStr">
         <is>
-          <t>Biz021</t>
+          <t>ORG-SH-001</t>
         </is>
       </c>
       <c r="D8" s="17" t="inlineStr">
         <is>
-          <t>盘轴车间</t>
-        </is>
-      </c>
-      <c r="E8" s="17" t="inlineStr"/>
+          <t>20-盘轴厂</t>
+        </is>
+      </c>
+      <c r="E8" s="17" t="inlineStr">
+        <is>
+          <t>负责盘轴组件加工、平衡与终检。</t>
+        </is>
+      </c>
       <c r="F8" s="17" t="inlineStr">
         <is>
-          <t>盘轴车间</t>
+          <t>盘轴厂</t>
         </is>
       </c>
       <c r="G8" s="17" t="inlineStr">
         <is>
-          <t>车间</t>
+          <t>工厂</t>
         </is>
       </c>
       <c r="H8" s="17" t="inlineStr">
         <is>
-          <t>Adm020</t>
-        </is>
-      </c>
-      <c r="I8" s="17" t="inlineStr"/>
+          <t>ADM-SH-001</t>
+        </is>
+      </c>
+      <c r="I8" s="17" t="inlineStr">
+        <is>
+          <t>机械加工专业</t>
+        </is>
+      </c>
       <c r="J8" s="17" t="inlineStr">
         <is>
           <t>MOM-SEED</t>
@@ -2538,7 +2546,7 @@
       </c>
       <c r="K8" s="17" t="inlineStr">
         <is>
-          <t>Biz021</t>
+          <t>ORG-SH-001</t>
         </is>
       </c>
       <c r="L8" s="17" t="inlineStr"/>
@@ -2546,7 +2554,7 @@
     <row r="9">
       <c r="A9" s="17" t="inlineStr">
         <is>
-          <t>Biz021</t>
+          <t>ORG-SH-001</t>
         </is>
       </c>
       <c r="B9" s="17" t="inlineStr">
@@ -2556,28 +2564,28 @@
       </c>
       <c r="C9" s="17" t="inlineStr">
         <is>
-          <t>Biz022</t>
+          <t>ORG-SH-WS-001</t>
         </is>
       </c>
       <c r="D9" s="17" t="inlineStr">
         <is>
-          <t>盘轴加工班组</t>
+          <t>盘轴车间</t>
         </is>
       </c>
       <c r="E9" s="17" t="inlineStr"/>
       <c r="F9" s="17" t="inlineStr">
         <is>
-          <t>盘轴加工</t>
+          <t>盘轴车间</t>
         </is>
       </c>
       <c r="G9" s="17" t="inlineStr">
         <is>
-          <t>班组</t>
+          <t>车间</t>
         </is>
       </c>
       <c r="H9" s="17" t="inlineStr">
         <is>
-          <t>Adm020</t>
+          <t>ADM-SH-001</t>
         </is>
       </c>
       <c r="I9" s="17" t="inlineStr"/>
@@ -2588,7 +2596,7 @@
       </c>
       <c r="K9" s="17" t="inlineStr">
         <is>
-          <t>Biz022</t>
+          <t>ORG-SH-WS-001</t>
         </is>
       </c>
       <c r="L9" s="17" t="inlineStr"/>
@@ -2596,7 +2604,7 @@
     <row r="10">
       <c r="A10" s="17" t="inlineStr">
         <is>
-          <t>Biz021</t>
+          <t>ORG-SH-WS-001</t>
         </is>
       </c>
       <c r="B10" s="17" t="inlineStr">
@@ -2606,18 +2614,18 @@
       </c>
       <c r="C10" s="17" t="inlineStr">
         <is>
-          <t>Biz023</t>
+          <t>ORG-SH-TM-001</t>
         </is>
       </c>
       <c r="D10" s="17" t="inlineStr">
         <is>
-          <t>盘轴检验班组</t>
+          <t>盘轴班组</t>
         </is>
       </c>
       <c r="E10" s="17" t="inlineStr"/>
       <c r="F10" s="17" t="inlineStr">
         <is>
-          <t>盘轴检验</t>
+          <t>盘轴班组</t>
         </is>
       </c>
       <c r="G10" s="17" t="inlineStr">
@@ -2627,7 +2635,7 @@
       </c>
       <c r="H10" s="17" t="inlineStr">
         <is>
-          <t>Adm020</t>
+          <t>ADM-SH-001</t>
         </is>
       </c>
       <c r="I10" s="17" t="inlineStr"/>
@@ -2638,7 +2646,7 @@
       </c>
       <c r="K10" s="17" t="inlineStr">
         <is>
-          <t>Biz023</t>
+          <t>ORG-SH-TM-001</t>
         </is>
       </c>
       <c r="L10" s="17" t="inlineStr"/>
@@ -2646,7 +2654,7 @@
     <row r="11">
       <c r="A11" s="17" t="inlineStr">
         <is>
-          <t>Biz001</t>
+          <t>ORG-SH-WS-001</t>
         </is>
       </c>
       <c r="B11" s="17" t="inlineStr">
@@ -2656,39 +2664,31 @@
       </c>
       <c r="C11" s="17" t="inlineStr">
         <is>
-          <t>Biz030</t>
+          <t>ORG-SH-QC-001</t>
         </is>
       </c>
       <c r="D11" s="17" t="inlineStr">
         <is>
-          <t>30-叶片厂</t>
-        </is>
-      </c>
-      <c r="E11" s="17" t="inlineStr">
-        <is>
-          <t>负责叶片成型、涂层与叶片终检</t>
-        </is>
-      </c>
+          <t>盘轴检验组</t>
+        </is>
+      </c>
+      <c r="E11" s="17" t="inlineStr"/>
       <c r="F11" s="17" t="inlineStr">
         <is>
-          <t>叶片厂</t>
+          <t>盘轴检验</t>
         </is>
       </c>
       <c r="G11" s="17" t="inlineStr">
         <is>
-          <t>工厂</t>
+          <t>班组</t>
         </is>
       </c>
       <c r="H11" s="17" t="inlineStr">
         <is>
-          <t>Adm030</t>
-        </is>
-      </c>
-      <c r="I11" s="17" t="inlineStr">
-        <is>
-          <t>机械加工专业</t>
-        </is>
-      </c>
+          <t>ADM-SH-001</t>
+        </is>
+      </c>
+      <c r="I11" s="17" t="inlineStr"/>
       <c r="J11" s="17" t="inlineStr">
         <is>
           <t>MOM-SEED</t>
@@ -2696,7 +2696,7 @@
       </c>
       <c r="K11" s="17" t="inlineStr">
         <is>
-          <t>Biz030</t>
+          <t>ORG-SH-QC-001</t>
         </is>
       </c>
       <c r="L11" s="17" t="inlineStr"/>
@@ -2704,7 +2704,7 @@
     <row r="12">
       <c r="A12" s="17" t="inlineStr">
         <is>
-          <t>Biz030</t>
+          <t>ORG-CORP-001</t>
         </is>
       </c>
       <c r="B12" s="17" t="inlineStr">
@@ -2714,31 +2714,39 @@
       </c>
       <c r="C12" s="17" t="inlineStr">
         <is>
-          <t>Biz031</t>
+          <t>ORG-BL-001</t>
         </is>
       </c>
       <c r="D12" s="17" t="inlineStr">
         <is>
-          <t>叶片车间</t>
-        </is>
-      </c>
-      <c r="E12" s="17" t="inlineStr"/>
+          <t>30-叶片厂</t>
+        </is>
+      </c>
+      <c r="E12" s="17" t="inlineStr">
+        <is>
+          <t>负责叶片成型、涂层与终检。</t>
+        </is>
+      </c>
       <c r="F12" s="17" t="inlineStr">
         <is>
-          <t>叶片车间</t>
+          <t>叶片厂</t>
         </is>
       </c>
       <c r="G12" s="17" t="inlineStr">
         <is>
-          <t>车间</t>
+          <t>工厂</t>
         </is>
       </c>
       <c r="H12" s="17" t="inlineStr">
         <is>
-          <t>Adm030</t>
-        </is>
-      </c>
-      <c r="I12" s="17" t="inlineStr"/>
+          <t>ADM-BL-001</t>
+        </is>
+      </c>
+      <c r="I12" s="17" t="inlineStr">
+        <is>
+          <t>机械加工专业</t>
+        </is>
+      </c>
       <c r="J12" s="17" t="inlineStr">
         <is>
           <t>MOM-SEED</t>
@@ -2746,7 +2754,7 @@
       </c>
       <c r="K12" s="17" t="inlineStr">
         <is>
-          <t>Biz031</t>
+          <t>ORG-BL-001</t>
         </is>
       </c>
       <c r="L12" s="17" t="inlineStr"/>
@@ -2754,7 +2762,7 @@
     <row r="13">
       <c r="A13" s="17" t="inlineStr">
         <is>
-          <t>Biz031</t>
+          <t>ORG-BL-001</t>
         </is>
       </c>
       <c r="B13" s="17" t="inlineStr">
@@ -2764,28 +2772,28 @@
       </c>
       <c r="C13" s="17" t="inlineStr">
         <is>
-          <t>Biz032</t>
+          <t>ORG-BL-WS-001</t>
         </is>
       </c>
       <c r="D13" s="17" t="inlineStr">
         <is>
-          <t>叶片加工班组</t>
+          <t>叶片车间</t>
         </is>
       </c>
       <c r="E13" s="17" t="inlineStr"/>
       <c r="F13" s="17" t="inlineStr">
         <is>
-          <t>叶片加工</t>
+          <t>叶片车间</t>
         </is>
       </c>
       <c r="G13" s="17" t="inlineStr">
         <is>
-          <t>班组</t>
+          <t>车间</t>
         </is>
       </c>
       <c r="H13" s="17" t="inlineStr">
         <is>
-          <t>Adm030</t>
+          <t>ADM-BL-001</t>
         </is>
       </c>
       <c r="I13" s="17" t="inlineStr"/>
@@ -2796,7 +2804,7 @@
       </c>
       <c r="K13" s="17" t="inlineStr">
         <is>
-          <t>Biz032</t>
+          <t>ORG-BL-WS-001</t>
         </is>
       </c>
       <c r="L13" s="17" t="inlineStr"/>
@@ -2804,7 +2812,7 @@
     <row r="14">
       <c r="A14" s="17" t="inlineStr">
         <is>
-          <t>Biz031</t>
+          <t>ORG-BL-WS-001</t>
         </is>
       </c>
       <c r="B14" s="17" t="inlineStr">
@@ -2814,18 +2822,18 @@
       </c>
       <c r="C14" s="17" t="inlineStr">
         <is>
-          <t>Biz033</t>
+          <t>ORG-BL-TM-001</t>
         </is>
       </c>
       <c r="D14" s="17" t="inlineStr">
         <is>
-          <t>叶片检验班组</t>
+          <t>叶片班组</t>
         </is>
       </c>
       <c r="E14" s="17" t="inlineStr"/>
       <c r="F14" s="17" t="inlineStr">
         <is>
-          <t>叶片检验</t>
+          <t>叶片班组</t>
         </is>
       </c>
       <c r="G14" s="17" t="inlineStr">
@@ -2835,7 +2843,7 @@
       </c>
       <c r="H14" s="17" t="inlineStr">
         <is>
-          <t>Adm030</t>
+          <t>ADM-BL-001</t>
         </is>
       </c>
       <c r="I14" s="17" t="inlineStr"/>
@@ -2846,7 +2854,7 @@
       </c>
       <c r="K14" s="17" t="inlineStr">
         <is>
-          <t>Biz033</t>
+          <t>ORG-BL-TM-001</t>
         </is>
       </c>
       <c r="L14" s="17" t="inlineStr"/>
@@ -2854,7 +2862,7 @@
     <row r="15">
       <c r="A15" s="17" t="inlineStr">
         <is>
-          <t>Biz001</t>
+          <t>ORG-BL-WS-001</t>
         </is>
       </c>
       <c r="B15" s="17" t="inlineStr">
@@ -2864,39 +2872,31 @@
       </c>
       <c r="C15" s="17" t="inlineStr">
         <is>
-          <t>Biz040</t>
+          <t>ORG-BL-QC-001</t>
         </is>
       </c>
       <c r="D15" s="17" t="inlineStr">
         <is>
-          <t>40-装配厂</t>
-        </is>
-      </c>
-      <c r="E15" s="17" t="inlineStr">
-        <is>
-          <t>负责整机装配、试车与交付放行</t>
-        </is>
-      </c>
+          <t>叶片检验组</t>
+        </is>
+      </c>
+      <c r="E15" s="17" t="inlineStr"/>
       <c r="F15" s="17" t="inlineStr">
         <is>
-          <t>装配厂</t>
+          <t>叶片检验</t>
         </is>
       </c>
       <c r="G15" s="17" t="inlineStr">
         <is>
-          <t>工厂</t>
+          <t>班组</t>
         </is>
       </c>
       <c r="H15" s="17" t="inlineStr">
         <is>
-          <t>Adm040</t>
-        </is>
-      </c>
-      <c r="I15" s="17" t="inlineStr">
-        <is>
-          <t>装配专业</t>
-        </is>
-      </c>
+          <t>ADM-BL-001</t>
+        </is>
+      </c>
+      <c r="I15" s="17" t="inlineStr"/>
       <c r="J15" s="17" t="inlineStr">
         <is>
           <t>MOM-SEED</t>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K15" s="17" t="inlineStr">
         <is>
-          <t>Biz040</t>
+          <t>ORG-BL-QC-001</t>
         </is>
       </c>
       <c r="L15" s="17" t="inlineStr"/>
@@ -2912,7 +2912,7 @@
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
         <is>
-          <t>Biz040</t>
+          <t>ORG-CORP-001</t>
         </is>
       </c>
       <c r="B16" s="17" t="inlineStr">
@@ -2922,31 +2922,39 @@
       </c>
       <c r="C16" s="17" t="inlineStr">
         <is>
-          <t>Biz041</t>
+          <t>ORG-AS-001</t>
         </is>
       </c>
       <c r="D16" s="17" t="inlineStr">
         <is>
-          <t>总装试车车间</t>
-        </is>
-      </c>
-      <c r="E16" s="17" t="inlineStr"/>
+          <t>40-装配厂</t>
+        </is>
+      </c>
+      <c r="E16" s="17" t="inlineStr">
+        <is>
+          <t>负责总装、试车、完工入库与交付放行。</t>
+        </is>
+      </c>
       <c r="F16" s="17" t="inlineStr">
         <is>
-          <t>总装试车</t>
+          <t>装配厂</t>
         </is>
       </c>
       <c r="G16" s="17" t="inlineStr">
         <is>
-          <t>车间</t>
+          <t>工厂</t>
         </is>
       </c>
       <c r="H16" s="17" t="inlineStr">
         <is>
-          <t>Adm040</t>
-        </is>
-      </c>
-      <c r="I16" s="17" t="inlineStr"/>
+          <t>ADM-AS-001</t>
+        </is>
+      </c>
+      <c r="I16" s="17" t="inlineStr">
+        <is>
+          <t>装配专业</t>
+        </is>
+      </c>
       <c r="J16" s="17" t="inlineStr">
         <is>
           <t>MOM-SEED</t>
@@ -2954,7 +2962,7 @@
       </c>
       <c r="K16" s="17" t="inlineStr">
         <is>
-          <t>Biz041</t>
+          <t>ORG-AS-001</t>
         </is>
       </c>
       <c r="L16" s="17" t="inlineStr"/>
@@ -2962,7 +2970,7 @@
     <row r="17">
       <c r="A17" s="17" t="inlineStr">
         <is>
-          <t>Biz041</t>
+          <t>ORG-AS-001</t>
         </is>
       </c>
       <c r="B17" s="17" t="inlineStr">
@@ -2972,28 +2980,28 @@
       </c>
       <c r="C17" s="17" t="inlineStr">
         <is>
-          <t>Biz042</t>
+          <t>ORG-AS-WS-001</t>
         </is>
       </c>
       <c r="D17" s="17" t="inlineStr">
         <is>
-          <t>总装班组</t>
+          <t>总装车间</t>
         </is>
       </c>
       <c r="E17" s="17" t="inlineStr"/>
       <c r="F17" s="17" t="inlineStr">
         <is>
-          <t>总装班组</t>
+          <t>总装车间</t>
         </is>
       </c>
       <c r="G17" s="17" t="inlineStr">
         <is>
-          <t>班组</t>
+          <t>车间</t>
         </is>
       </c>
       <c r="H17" s="17" t="inlineStr">
         <is>
-          <t>Adm040</t>
+          <t>ADM-AS-001</t>
         </is>
       </c>
       <c r="I17" s="17" t="inlineStr"/>
@@ -3004,7 +3012,7 @@
       </c>
       <c r="K17" s="17" t="inlineStr">
         <is>
-          <t>Biz042</t>
+          <t>ORG-AS-WS-001</t>
         </is>
       </c>
       <c r="L17" s="17" t="inlineStr"/>
@@ -3012,7 +3020,7 @@
     <row r="18">
       <c r="A18" s="17" t="inlineStr">
         <is>
-          <t>Biz041</t>
+          <t>ORG-AS-WS-001</t>
         </is>
       </c>
       <c r="B18" s="17" t="inlineStr">
@@ -3022,18 +3030,18 @@
       </c>
       <c r="C18" s="17" t="inlineStr">
         <is>
-          <t>Biz043</t>
+          <t>ORG-AS-TM-001</t>
         </is>
       </c>
       <c r="D18" s="17" t="inlineStr">
         <is>
-          <t>试车放行班组</t>
+          <t>总装班组</t>
         </is>
       </c>
       <c r="E18" s="17" t="inlineStr"/>
       <c r="F18" s="17" t="inlineStr">
         <is>
-          <t>试车放行</t>
+          <t>总装班组</t>
         </is>
       </c>
       <c r="G18" s="17" t="inlineStr">
@@ -3043,7 +3051,7 @@
       </c>
       <c r="H18" s="17" t="inlineStr">
         <is>
-          <t>Adm040</t>
+          <t>ADM-AS-001</t>
         </is>
       </c>
       <c r="I18" s="17" t="inlineStr"/>
@@ -3054,7 +3062,7 @@
       </c>
       <c r="K18" s="17" t="inlineStr">
         <is>
-          <t>Biz043</t>
+          <t>ORG-AS-TM-001</t>
         </is>
       </c>
       <c r="L18" s="17" t="inlineStr"/>
@@ -3062,7 +3070,7 @@
     <row r="19">
       <c r="A19" s="17" t="inlineStr">
         <is>
-          <t>Biz001</t>
+          <t>ORG-AS-WS-001</t>
         </is>
       </c>
       <c r="B19" s="17" t="inlineStr">
@@ -3072,39 +3080,31 @@
       </c>
       <c r="C19" s="17" t="inlineStr">
         <is>
-          <t>Biz900</t>
+          <t>ORG-AS-QC-001</t>
         </is>
       </c>
       <c r="D19" s="17" t="inlineStr">
         <is>
-          <t>生产部</t>
-        </is>
-      </c>
-      <c r="E19" s="17" t="inlineStr">
-        <is>
-          <t>用于生产部持单的一级工艺、厂际协同计划与多工厂排产总览。</t>
-        </is>
-      </c>
+          <t>总装检验组</t>
+        </is>
+      </c>
+      <c r="E19" s="17" t="inlineStr"/>
       <c r="F19" s="17" t="inlineStr">
         <is>
-          <t>生产部</t>
+          <t>总装检验</t>
         </is>
       </c>
       <c r="G19" s="17" t="inlineStr">
         <is>
-          <t>工厂</t>
+          <t>班组</t>
         </is>
       </c>
       <c r="H19" s="17" t="inlineStr">
         <is>
-          <t>Adm900</t>
-        </is>
-      </c>
-      <c r="I19" s="17" t="inlineStr">
-        <is>
-          <t>装配专业</t>
-        </is>
-      </c>
+          <t>ADM-AS-001</t>
+        </is>
+      </c>
+      <c r="I19" s="17" t="inlineStr"/>
       <c r="J19" s="17" t="inlineStr">
         <is>
           <t>MOM-SEED</t>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="K19" s="17" t="inlineStr">
         <is>
-          <t>Biz900</t>
+          <t>ORG-AS-QC-001</t>
         </is>
       </c>
       <c r="L19" s="17" t="inlineStr"/>
@@ -4381,12 +4381,12 @@
     <row r="2">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>K2001</t>
+          <t>zhangqiang</t>
         </is>
       </c>
       <c r="B2" s="17" t="inlineStr">
         <is>
-          <t>顾明川</t>
+          <t>张强</t>
         </is>
       </c>
       <c r="C2" s="17" t="inlineStr">
@@ -4415,35 +4415,35 @@
       </c>
       <c r="K2" s="17" t="inlineStr">
         <is>
-          <t>K2001</t>
+          <t>zhangqiang</t>
         </is>
       </c>
       <c r="L2" s="17" t="inlineStr"/>
       <c r="M2" s="17" t="inlineStr">
         <is>
-          <t>Adm900</t>
+          <t>ADM-PD-001</t>
         </is>
       </c>
       <c r="N2" s="17" t="inlineStr">
         <is>
-          <t>Biz900</t>
+          <t>ORG-PD-001</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="17" t="inlineStr">
         <is>
-          <t>K2002</t>
+          <t>liumin</t>
         </is>
       </c>
       <c r="B3" s="17" t="inlineStr">
         <is>
-          <t>林清越</t>
+          <t>刘敏</t>
         </is>
       </c>
       <c r="C3" s="17" t="inlineStr">
         <is>
-          <t>主计划员</t>
+          <t>计划员</t>
         </is>
       </c>
       <c r="D3" s="17" t="inlineStr">
@@ -4467,35 +4467,35 @@
       </c>
       <c r="K3" s="17" t="inlineStr">
         <is>
-          <t>K2002</t>
+          <t>liumin</t>
         </is>
       </c>
       <c r="L3" s="17" t="inlineStr"/>
       <c r="M3" s="17" t="inlineStr">
         <is>
-          <t>Adm900</t>
+          <t>ADM-PD-001</t>
         </is>
       </c>
       <c r="N3" s="17" t="inlineStr">
         <is>
-          <t>Biz900</t>
+          <t>ORG-PD-001</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="17" t="inlineStr">
         <is>
-          <t>K2003</t>
+          <t>chengang</t>
         </is>
       </c>
       <c r="B4" s="17" t="inlineStr">
         <is>
-          <t>许知行</t>
+          <t>陈刚</t>
         </is>
       </c>
       <c r="C4" s="17" t="inlineStr">
         <is>
-          <t>工艺工程师</t>
+          <t>机加班组长</t>
         </is>
       </c>
       <c r="D4" s="17" t="inlineStr">
@@ -4519,35 +4519,35 @@
       </c>
       <c r="K4" s="17" t="inlineStr">
         <is>
-          <t>K2003</t>
+          <t>chengang</t>
         </is>
       </c>
       <c r="L4" s="17" t="inlineStr"/>
       <c r="M4" s="17" t="inlineStr">
         <is>
-          <t>Adm900</t>
+          <t>ADM-MC-001</t>
         </is>
       </c>
       <c r="N4" s="17" t="inlineStr">
         <is>
-          <t>Biz900</t>
+          <t>ORG-MC-TM-001</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="inlineStr">
         <is>
-          <t>K2004</t>
+          <t>wanglei</t>
         </is>
       </c>
       <c r="B5" s="17" t="inlineStr">
         <is>
-          <t>沈安和</t>
+          <t>王磊</t>
         </is>
       </c>
       <c r="C5" s="17" t="inlineStr">
         <is>
-          <t>机加班组长</t>
+          <t>仓库管理员</t>
         </is>
       </c>
       <c r="D5" s="17" t="inlineStr">
@@ -4571,35 +4571,35 @@
       </c>
       <c r="K5" s="17" t="inlineStr">
         <is>
-          <t>K2004</t>
+          <t>wanglei</t>
         </is>
       </c>
       <c r="L5" s="17" t="inlineStr"/>
       <c r="M5" s="17" t="inlineStr">
         <is>
-          <t>Adm010</t>
+          <t>ADM-AS-001</t>
         </is>
       </c>
       <c r="N5" s="17" t="inlineStr">
         <is>
-          <t>Biz012</t>
+          <t>ORG-AS-001</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="17" t="inlineStr">
         <is>
-          <t>K2005</t>
+          <t>zhaoyun</t>
         </is>
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
-          <t>宋言舟</t>
+          <t>赵云</t>
         </is>
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t>机加操作工</t>
+          <t>装配班组长</t>
         </is>
       </c>
       <c r="D6" s="17" t="inlineStr">
@@ -4623,35 +4623,35 @@
       </c>
       <c r="K6" s="17" t="inlineStr">
         <is>
-          <t>K2005</t>
+          <t>zhaoyun</t>
         </is>
       </c>
       <c r="L6" s="17" t="inlineStr"/>
       <c r="M6" s="17" t="inlineStr">
         <is>
-          <t>Adm010</t>
+          <t>ADM-AS-001</t>
         </is>
       </c>
       <c r="N6" s="17" t="inlineStr">
         <is>
-          <t>Biz012</t>
+          <t>ORG-AS-TM-001</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="17" t="inlineStr">
         <is>
-          <t>K2006</t>
+          <t>qianfeng</t>
         </is>
       </c>
       <c r="B7" s="17" t="inlineStr">
         <is>
-          <t>顾若宁</t>
+          <t>钱峰</t>
         </is>
       </c>
       <c r="C7" s="17" t="inlineStr">
         <is>
-          <t>机加检验员</t>
+          <t>装配操作工</t>
         </is>
       </c>
       <c r="D7" s="17" t="inlineStr">
@@ -4663,7 +4663,7 @@
       <c r="F7" s="17" t="inlineStr"/>
       <c r="G7" s="17" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="H7" s="17" t="inlineStr"/>
@@ -4675,35 +4675,35 @@
       </c>
       <c r="K7" s="17" t="inlineStr">
         <is>
-          <t>K2006</t>
+          <t>qianfeng</t>
         </is>
       </c>
       <c r="L7" s="17" t="inlineStr"/>
       <c r="M7" s="17" t="inlineStr">
         <is>
-          <t>Adm010</t>
+          <t>ADM-AS-001</t>
         </is>
       </c>
       <c r="N7" s="17" t="inlineStr">
         <is>
-          <t>Biz013</t>
+          <t>ORG-AS-TM-001</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="17" t="inlineStr">
         <is>
-          <t>K2007</t>
+          <t>sunjie</t>
         </is>
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>唐书远</t>
+          <t>孙洁</t>
         </is>
       </c>
       <c r="C8" s="17" t="inlineStr">
         <is>
-          <t>仓库管理员</t>
+          <t>检验员</t>
         </is>
       </c>
       <c r="D8" s="17" t="inlineStr">
@@ -4715,7 +4715,7 @@
       <c r="F8" s="17" t="inlineStr"/>
       <c r="G8" s="17" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="H8" s="17" t="inlineStr"/>
@@ -4727,30 +4727,30 @@
       </c>
       <c r="K8" s="17" t="inlineStr">
         <is>
-          <t>K2007</t>
+          <t>sunjie</t>
         </is>
       </c>
       <c r="L8" s="17" t="inlineStr"/>
       <c r="M8" s="17" t="inlineStr">
         <is>
-          <t>Adm010</t>
+          <t>ADM-AS-001</t>
         </is>
       </c>
       <c r="N8" s="17" t="inlineStr">
         <is>
-          <t>Biz010</t>
+          <t>ORG-AS-QC-001</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="17" t="inlineStr">
         <is>
-          <t>K2008</t>
+          <t>hanbo</t>
         </is>
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>周景程</t>
+          <t>韩博</t>
         </is>
       </c>
       <c r="C9" s="17" t="inlineStr">
@@ -4779,35 +4779,35 @@
       </c>
       <c r="K9" s="17" t="inlineStr">
         <is>
-          <t>K2008</t>
+          <t>hanbo</t>
         </is>
       </c>
       <c r="L9" s="17" t="inlineStr"/>
       <c r="M9" s="17" t="inlineStr">
         <is>
-          <t>Adm020</t>
+          <t>ADM-SH-001</t>
         </is>
       </c>
       <c r="N9" s="17" t="inlineStr">
         <is>
-          <t>Biz022</t>
+          <t>ORG-SH-TM-001</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="17" t="inlineStr">
         <is>
-          <t>K2009</t>
+          <t>linna</t>
         </is>
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>陆知夏</t>
+          <t>林娜</t>
         </is>
       </c>
       <c r="C10" s="17" t="inlineStr">
         <is>
-          <t>盘轴操作工</t>
+          <t>叶片班组长</t>
         </is>
       </c>
       <c r="D10" s="17" t="inlineStr">
@@ -4831,35 +4831,35 @@
       </c>
       <c r="K10" s="17" t="inlineStr">
         <is>
-          <t>K2009</t>
+          <t>linna</t>
         </is>
       </c>
       <c r="L10" s="17" t="inlineStr"/>
       <c r="M10" s="17" t="inlineStr">
         <is>
-          <t>Adm020</t>
+          <t>ADM-BL-001</t>
         </is>
       </c>
       <c r="N10" s="17" t="inlineStr">
         <is>
-          <t>Biz022</t>
+          <t>ORG-BL-TM-001</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="17" t="inlineStr">
         <is>
-          <t>K2010</t>
+          <t>chenrui</t>
         </is>
       </c>
       <c r="B11" s="17" t="inlineStr">
         <is>
-          <t>韩以宁</t>
+          <t>陈睿</t>
         </is>
       </c>
       <c r="C11" s="17" t="inlineStr">
         <is>
-          <t>盘轴检验员</t>
+          <t>工艺工程师</t>
         </is>
       </c>
       <c r="D11" s="17" t="inlineStr">
@@ -4883,488 +4883,164 @@
       </c>
       <c r="K11" s="17" t="inlineStr">
         <is>
-          <t>K2010</t>
+          <t>chenrui</t>
         </is>
       </c>
       <c r="L11" s="17" t="inlineStr"/>
       <c r="M11" s="17" t="inlineStr">
         <is>
-          <t>Adm020</t>
+          <t>ADM-PD-001</t>
         </is>
       </c>
       <c r="N11" s="17" t="inlineStr">
         <is>
-          <t>Biz023</t>
+          <t>ORG-PD-001</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="17" t="inlineStr">
-        <is>
-          <t>K2011</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>乔云舒</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>仓库管理员</t>
-        </is>
-      </c>
-      <c r="D12" s="17" t="inlineStr">
-        <is>
-          <t>一般</t>
-        </is>
-      </c>
+      <c r="A12" s="17" t="inlineStr"/>
+      <c r="B12" s="17" t="inlineStr"/>
+      <c r="C12" s="17" t="inlineStr"/>
+      <c r="D12" s="17" t="inlineStr"/>
       <c r="E12" s="17" t="inlineStr"/>
       <c r="F12" s="17" t="inlineStr"/>
-      <c r="G12" s="17" t="inlineStr">
-        <is>
-          <t>女</t>
-        </is>
-      </c>
+      <c r="G12" s="17" t="inlineStr"/>
       <c r="H12" s="17" t="inlineStr"/>
       <c r="I12" s="17" t="inlineStr"/>
-      <c r="J12" s="17" t="inlineStr">
-        <is>
-          <t>MOM-SEED</t>
-        </is>
-      </c>
-      <c r="K12" s="17" t="inlineStr">
-        <is>
-          <t>K2011</t>
-        </is>
-      </c>
+      <c r="J12" s="17" t="inlineStr"/>
+      <c r="K12" s="17" t="inlineStr"/>
       <c r="L12" s="17" t="inlineStr"/>
-      <c r="M12" s="17" t="inlineStr">
-        <is>
-          <t>Adm020</t>
-        </is>
-      </c>
-      <c r="N12" s="17" t="inlineStr">
-        <is>
-          <t>Biz020</t>
-        </is>
-      </c>
+      <c r="M12" s="17" t="inlineStr"/>
+      <c r="N12" s="17" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="inlineStr">
-        <is>
-          <t>K2012</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>温清妍</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>叶片班组长</t>
-        </is>
-      </c>
-      <c r="D13" s="17" t="inlineStr">
-        <is>
-          <t>一般</t>
-        </is>
-      </c>
+      <c r="A13" s="17" t="inlineStr"/>
+      <c r="B13" s="17" t="inlineStr"/>
+      <c r="C13" s="17" t="inlineStr"/>
+      <c r="D13" s="17" t="inlineStr"/>
       <c r="E13" s="17" t="inlineStr"/>
       <c r="F13" s="17" t="inlineStr"/>
-      <c r="G13" s="17" t="inlineStr">
-        <is>
-          <t>女</t>
-        </is>
-      </c>
+      <c r="G13" s="17" t="inlineStr"/>
       <c r="H13" s="17" t="inlineStr"/>
       <c r="I13" s="17" t="inlineStr"/>
-      <c r="J13" s="17" t="inlineStr">
-        <is>
-          <t>MOM-SEED</t>
-        </is>
-      </c>
-      <c r="K13" s="17" t="inlineStr">
-        <is>
-          <t>K2012</t>
-        </is>
-      </c>
+      <c r="J13" s="17" t="inlineStr"/>
+      <c r="K13" s="17" t="inlineStr"/>
       <c r="L13" s="17" t="inlineStr"/>
-      <c r="M13" s="17" t="inlineStr">
-        <is>
-          <t>Adm030</t>
-        </is>
-      </c>
-      <c r="N13" s="17" t="inlineStr">
-        <is>
-          <t>Biz032</t>
-        </is>
-      </c>
+      <c r="M13" s="17" t="inlineStr"/>
+      <c r="N13" s="17" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="inlineStr">
-        <is>
-          <t>K2013</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>郑承泽</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>叶片操作工</t>
-        </is>
-      </c>
-      <c r="D14" s="17" t="inlineStr">
-        <is>
-          <t>一般</t>
-        </is>
-      </c>
+      <c r="A14" s="17" t="inlineStr"/>
+      <c r="B14" s="17" t="inlineStr"/>
+      <c r="C14" s="17" t="inlineStr"/>
+      <c r="D14" s="17" t="inlineStr"/>
       <c r="E14" s="17" t="inlineStr"/>
       <c r="F14" s="17" t="inlineStr"/>
-      <c r="G14" s="17" t="inlineStr">
-        <is>
-          <t>男</t>
-        </is>
-      </c>
+      <c r="G14" s="17" t="inlineStr"/>
       <c r="H14" s="17" t="inlineStr"/>
       <c r="I14" s="17" t="inlineStr"/>
-      <c r="J14" s="17" t="inlineStr">
-        <is>
-          <t>MOM-SEED</t>
-        </is>
-      </c>
-      <c r="K14" s="17" t="inlineStr">
-        <is>
-          <t>K2013</t>
-        </is>
-      </c>
+      <c r="J14" s="17" t="inlineStr"/>
+      <c r="K14" s="17" t="inlineStr"/>
       <c r="L14" s="17" t="inlineStr"/>
-      <c r="M14" s="17" t="inlineStr">
-        <is>
-          <t>Adm030</t>
-        </is>
-      </c>
-      <c r="N14" s="17" t="inlineStr">
-        <is>
-          <t>Biz032</t>
-        </is>
-      </c>
+      <c r="M14" s="17" t="inlineStr"/>
+      <c r="N14" s="17" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="inlineStr">
-        <is>
-          <t>K2014</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>程可欣</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>叶片检验员</t>
-        </is>
-      </c>
-      <c r="D15" s="17" t="inlineStr">
-        <is>
-          <t>一般</t>
-        </is>
-      </c>
+      <c r="A15" s="17" t="inlineStr"/>
+      <c r="B15" s="17" t="inlineStr"/>
+      <c r="C15" s="17" t="inlineStr"/>
+      <c r="D15" s="17" t="inlineStr"/>
       <c r="E15" s="17" t="inlineStr"/>
       <c r="F15" s="17" t="inlineStr"/>
-      <c r="G15" s="17" t="inlineStr">
-        <is>
-          <t>女</t>
-        </is>
-      </c>
+      <c r="G15" s="17" t="inlineStr"/>
       <c r="H15" s="17" t="inlineStr"/>
       <c r="I15" s="17" t="inlineStr"/>
-      <c r="J15" s="17" t="inlineStr">
-        <is>
-          <t>MOM-SEED</t>
-        </is>
-      </c>
-      <c r="K15" s="17" t="inlineStr">
-        <is>
-          <t>K2014</t>
-        </is>
-      </c>
+      <c r="J15" s="17" t="inlineStr"/>
+      <c r="K15" s="17" t="inlineStr"/>
       <c r="L15" s="17" t="inlineStr"/>
-      <c r="M15" s="17" t="inlineStr">
-        <is>
-          <t>Adm030</t>
-        </is>
-      </c>
-      <c r="N15" s="17" t="inlineStr">
-        <is>
-          <t>Biz033</t>
-        </is>
-      </c>
+      <c r="M15" s="17" t="inlineStr"/>
+      <c r="N15" s="17" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
-        <is>
-          <t>K2015</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>谢闻笙</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t>仓库管理员</t>
-        </is>
-      </c>
-      <c r="D16" s="17" t="inlineStr">
-        <is>
-          <t>一般</t>
-        </is>
-      </c>
+      <c r="A16" s="17" t="inlineStr"/>
+      <c r="B16" s="17" t="inlineStr"/>
+      <c r="C16" s="17" t="inlineStr"/>
+      <c r="D16" s="17" t="inlineStr"/>
       <c r="E16" s="17" t="inlineStr"/>
       <c r="F16" s="17" t="inlineStr"/>
-      <c r="G16" s="17" t="inlineStr">
-        <is>
-          <t>男</t>
-        </is>
-      </c>
+      <c r="G16" s="17" t="inlineStr"/>
       <c r="H16" s="17" t="inlineStr"/>
       <c r="I16" s="17" t="inlineStr"/>
-      <c r="J16" s="17" t="inlineStr">
-        <is>
-          <t>MOM-SEED</t>
-        </is>
-      </c>
-      <c r="K16" s="17" t="inlineStr">
-        <is>
-          <t>K2015</t>
-        </is>
-      </c>
+      <c r="J16" s="17" t="inlineStr"/>
+      <c r="K16" s="17" t="inlineStr"/>
       <c r="L16" s="17" t="inlineStr"/>
-      <c r="M16" s="17" t="inlineStr">
-        <is>
-          <t>Adm030</t>
-        </is>
-      </c>
-      <c r="N16" s="17" t="inlineStr">
-        <is>
-          <t>Biz030</t>
-        </is>
-      </c>
+      <c r="M16" s="17" t="inlineStr"/>
+      <c r="N16" s="17" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="17" t="inlineStr">
-        <is>
-          <t>K2016</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>苏景明</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>装配班组长</t>
-        </is>
-      </c>
-      <c r="D17" s="17" t="inlineStr">
-        <is>
-          <t>一般</t>
-        </is>
-      </c>
+      <c r="A17" s="17" t="inlineStr"/>
+      <c r="B17" s="17" t="inlineStr"/>
+      <c r="C17" s="17" t="inlineStr"/>
+      <c r="D17" s="17" t="inlineStr"/>
       <c r="E17" s="17" t="inlineStr"/>
       <c r="F17" s="17" t="inlineStr"/>
-      <c r="G17" s="17" t="inlineStr">
-        <is>
-          <t>男</t>
-        </is>
-      </c>
+      <c r="G17" s="17" t="inlineStr"/>
       <c r="H17" s="17" t="inlineStr"/>
       <c r="I17" s="17" t="inlineStr"/>
-      <c r="J17" s="17" t="inlineStr">
-        <is>
-          <t>MOM-SEED</t>
-        </is>
-      </c>
-      <c r="K17" s="17" t="inlineStr">
-        <is>
-          <t>K2016</t>
-        </is>
-      </c>
+      <c r="J17" s="17" t="inlineStr"/>
+      <c r="K17" s="17" t="inlineStr"/>
       <c r="L17" s="17" t="inlineStr"/>
-      <c r="M17" s="17" t="inlineStr">
-        <is>
-          <t>Adm040</t>
-        </is>
-      </c>
-      <c r="N17" s="17" t="inlineStr">
-        <is>
-          <t>Biz042</t>
-        </is>
-      </c>
+      <c r="M17" s="17" t="inlineStr"/>
+      <c r="N17" s="17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="17" t="inlineStr">
-        <is>
-          <t>K2017</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>叶安宁</t>
-        </is>
-      </c>
-      <c r="C18" s="17" t="inlineStr">
-        <is>
-          <t>装配操作工</t>
-        </is>
-      </c>
-      <c r="D18" s="17" t="inlineStr">
-        <is>
-          <t>一般</t>
-        </is>
-      </c>
+      <c r="A18" s="17" t="inlineStr"/>
+      <c r="B18" s="17" t="inlineStr"/>
+      <c r="C18" s="17" t="inlineStr"/>
+      <c r="D18" s="17" t="inlineStr"/>
       <c r="E18" s="17" t="inlineStr"/>
       <c r="F18" s="17" t="inlineStr"/>
-      <c r="G18" s="17" t="inlineStr">
-        <is>
-          <t>女</t>
-        </is>
-      </c>
+      <c r="G18" s="17" t="inlineStr"/>
       <c r="H18" s="17" t="inlineStr"/>
       <c r="I18" s="17" t="inlineStr"/>
-      <c r="J18" s="17" t="inlineStr">
-        <is>
-          <t>MOM-SEED</t>
-        </is>
-      </c>
-      <c r="K18" s="17" t="inlineStr">
-        <is>
-          <t>K2017</t>
-        </is>
-      </c>
+      <c r="J18" s="17" t="inlineStr"/>
+      <c r="K18" s="17" t="inlineStr"/>
       <c r="L18" s="17" t="inlineStr"/>
-      <c r="M18" s="17" t="inlineStr">
-        <is>
-          <t>Adm040</t>
-        </is>
-      </c>
-      <c r="N18" s="17" t="inlineStr">
-        <is>
-          <t>Biz042</t>
-        </is>
-      </c>
+      <c r="M18" s="17" t="inlineStr"/>
+      <c r="N18" s="17" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="17" t="inlineStr">
-        <is>
-          <t>K2018</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>梁知远</t>
-        </is>
-      </c>
-      <c r="C19" s="17" t="inlineStr">
-        <is>
-          <t>检验员</t>
-        </is>
-      </c>
-      <c r="D19" s="17" t="inlineStr">
-        <is>
-          <t>一般</t>
-        </is>
-      </c>
+      <c r="A19" s="17" t="inlineStr"/>
+      <c r="B19" s="17" t="inlineStr"/>
+      <c r="C19" s="17" t="inlineStr"/>
+      <c r="D19" s="17" t="inlineStr"/>
       <c r="E19" s="17" t="inlineStr"/>
       <c r="F19" s="17" t="inlineStr"/>
-      <c r="G19" s="17" t="inlineStr">
-        <is>
-          <t>男</t>
-        </is>
-      </c>
+      <c r="G19" s="17" t="inlineStr"/>
       <c r="H19" s="17" t="inlineStr"/>
       <c r="I19" s="17" t="inlineStr"/>
-      <c r="J19" s="17" t="inlineStr">
-        <is>
-          <t>MOM-SEED</t>
-        </is>
-      </c>
-      <c r="K19" s="17" t="inlineStr">
-        <is>
-          <t>K2018</t>
-        </is>
-      </c>
+      <c r="J19" s="17" t="inlineStr"/>
+      <c r="K19" s="17" t="inlineStr"/>
       <c r="L19" s="17" t="inlineStr"/>
-      <c r="M19" s="17" t="inlineStr">
-        <is>
-          <t>Adm040</t>
-        </is>
-      </c>
-      <c r="N19" s="17" t="inlineStr">
-        <is>
-          <t>Biz043</t>
-        </is>
-      </c>
+      <c r="M19" s="17" t="inlineStr"/>
+      <c r="N19" s="17" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="17" t="inlineStr">
-        <is>
-          <t>K2019</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>秦若衡</t>
-        </is>
-      </c>
-      <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>仓库管理员</t>
-        </is>
-      </c>
-      <c r="D20" s="17" t="inlineStr">
-        <is>
-          <t>一般</t>
-        </is>
-      </c>
+      <c r="A20" s="17" t="inlineStr"/>
+      <c r="B20" s="17" t="inlineStr"/>
+      <c r="C20" s="17" t="inlineStr"/>
+      <c r="D20" s="17" t="inlineStr"/>
       <c r="E20" s="17" t="inlineStr"/>
       <c r="F20" s="17" t="inlineStr"/>
-      <c r="G20" s="17" t="inlineStr">
-        <is>
-          <t>女</t>
-        </is>
-      </c>
+      <c r="G20" s="17" t="inlineStr"/>
       <c r="H20" s="17" t="inlineStr"/>
       <c r="I20" s="17" t="inlineStr"/>
-      <c r="J20" s="17" t="inlineStr">
-        <is>
-          <t>MOM-SEED</t>
-        </is>
-      </c>
-      <c r="K20" s="17" t="inlineStr">
-        <is>
-          <t>K2019</t>
-        </is>
-      </c>
+      <c r="J20" s="17" t="inlineStr"/>
+      <c r="K20" s="17" t="inlineStr"/>
       <c r="L20" s="17" t="inlineStr"/>
-      <c r="M20" s="17" t="inlineStr">
-        <is>
-          <t>Adm040</t>
-        </is>
-      </c>
-      <c r="N20" s="17" t="inlineStr">
-        <is>
-          <t>Biz040</t>
-        </is>
-      </c>
+      <c r="M20" s="17" t="inlineStr"/>
+      <c r="N20" s="17" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="17" t="inlineStr"/>
